--- a/outputs/monitor_xlsx/20260313.xlsx
+++ b/outputs/monitor_xlsx/20260313.xlsx
@@ -544,10 +544,6 @@
           <t>+0.16%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.24%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.28%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.05%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-0.37%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>+3.11%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,7 +671,6 @@
           <t>-580.17億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-475.73億</t>
@@ -733,7 +708,6 @@
           <t>-0.44億</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>59.78億</t>
@@ -744,8 +718,6 @@
           <t>298.89億</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,15 +735,11 @@
           <t>158.91%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>136.11%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -789,11 +757,6 @@
           <t>-673.42億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,15 +774,11 @@
           <t>15640口</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>14687口</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,7 +796,6 @@
           <t>-64.03億</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>-12.59億</t>
@@ -942,10 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1067,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1102,6 +1056,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1821,7 +1776,7 @@
         <v>-501</v>
       </c>
       <c r="K13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>8</v>
@@ -2335,6 +2290,112 @@
       <c r="W21" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6285</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>457</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-570</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>292</v>
+      </c>
+      <c r="J22" t="n">
+        <v>23</v>
+      </c>
+      <c r="K22" t="n">
+        <v>255</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1252</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-8986</v>
+      </c>
+      <c r="N22" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1530</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-162</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1040</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-157</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>59</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3137</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15704</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-106259</v>
+      </c>
+      <c r="N23" t="n">
+        <v>20</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏多</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260313.xlsx
+++ b/outputs/monitor_xlsx/20260313.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,220 +526,232 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.28%</t>
+          <t>33400.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
+          <t>-0.54%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5052.5$</t>
+          <t>312.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.24%</t>
-        </is>
-      </c>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+0.28%</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7646.64</t>
+          <t>4.28%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>5052.5$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.37%</t>
-        </is>
-      </c>
+          <t>-1.24%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>原物料</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI原油期貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>98.71$</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+3.11%</t>
-        </is>
-      </c>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-580.17億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-475.73億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-2378.67億</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-221.82億</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-4436.48億</t>
-        </is>
-      </c>
+          <t>7646.64</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.44億</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>59.78億</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>298.89億</t>
-        </is>
-      </c>
+          <t>27.19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>158.91%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>136.11%</t>
-        </is>
-      </c>
+          <t>98.71$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+3.11%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -749,12 +761,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-673.42億</t>
+          <t>-580.17億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-496.04億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-2480.18億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -766,52 +799,135 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>投信現貨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15640口</t>
-        </is>
-      </c>
+          <t>-0.44億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14687口</t>
-        </is>
-      </c>
+          <t>47.91億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>239.53億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-673.42億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15640口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>14687口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-64.03億</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-12.59億</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-62.93億</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>-8.05億</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>-161.1億</t>
         </is>
@@ -860,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-475.73億</t>
+          <t>-496.04億</t>
         </is>
       </c>
     </row>
@@ -872,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2378.67億</t>
+          <t>-2480.18億</t>
         </is>
       </c>
     </row>
@@ -884,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-221.82億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -896,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-4436.48億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>59.78億</t>
+          <t>47.91億</t>
         </is>
       </c>
     </row>
@@ -920,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>298.89億</t>
+          <t>239.53億</t>
         </is>
       </c>
     </row>
@@ -994,7 +1114,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>136.11%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1039,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1135,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1203,13 +1316,13 @@
         <v>-58613</v>
       </c>
       <c r="H4" t="n">
-        <v>-407526</v>
+        <v>-331939</v>
       </c>
       <c r="I4" t="n">
         <v>65</v>
       </c>
       <c r="J4" t="n">
-        <v>16415</v>
+        <v>13115</v>
       </c>
       <c r="K4" t="n">
         <v>15007</v>
@@ -1218,20 +1331,12 @@
         <v>13375</v>
       </c>
       <c r="M4" t="n">
-        <v>65854</v>
+        <v>54244</v>
       </c>
       <c r="N4" t="n">
         <v>-4446750</v>
       </c>
-      <c r="O4" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1266,13 +1371,13 @@
         <v>-96</v>
       </c>
       <c r="H5" t="n">
-        <v>-1611</v>
+        <v>-632</v>
       </c>
       <c r="I5" t="n">
         <v>-78</v>
       </c>
       <c r="J5" t="n">
-        <v>-716</v>
+        <v>-568</v>
       </c>
       <c r="K5" t="n">
         <v>75</v>
@@ -1281,20 +1386,12 @@
         <v>2789</v>
       </c>
       <c r="M5" t="n">
-        <v>14021</v>
+        <v>11081</v>
       </c>
       <c r="N5" t="n">
         <v>-78814</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1329,13 +1426,13 @@
         <v>268</v>
       </c>
       <c r="H6" t="n">
-        <v>-684</v>
+        <v>93</v>
       </c>
       <c r="I6" t="n">
         <v>-178</v>
       </c>
       <c r="J6" t="n">
-        <v>1509</v>
+        <v>1365</v>
       </c>
       <c r="K6" t="n">
         <v>210</v>
@@ -1344,20 +1441,12 @@
         <v>5871</v>
       </c>
       <c r="M6" t="n">
-        <v>29190</v>
+        <v>23454</v>
       </c>
       <c r="N6" t="n">
         <v>-648994</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1392,13 +1481,13 @@
         <v>-12743</v>
       </c>
       <c r="H7" t="n">
-        <v>-63752</v>
+        <v>-52825</v>
       </c>
       <c r="I7" t="n">
         <v>-133</v>
       </c>
       <c r="J7" t="n">
-        <v>4376</v>
+        <v>3430</v>
       </c>
       <c r="K7" t="n">
         <v>1133</v>
@@ -1407,20 +1496,12 @@
         <v>25620</v>
       </c>
       <c r="M7" t="n">
-        <v>122657</v>
+        <v>99025</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
-      <c r="O7" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1429,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,47 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6551</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>-2430</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-832</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-142</v>
+      </c>
+      <c r="J8" t="n">
+        <v>408</v>
+      </c>
+      <c r="K8" t="n">
         <v>109</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>172609</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>-17436</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3860</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-105</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-3095</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3484</v>
-      </c>
       <c r="L8" t="n">
-        <v>127508</v>
+        <v>2056</v>
       </c>
       <c r="M8" t="n">
-        <v>628562</v>
+        <v>7358</v>
       </c>
       <c r="N8" t="n">
-        <v>-1114939</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140185</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1492,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1506,47 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2705</v>
+        <v>1530</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>4.04</v>
+        <v>2.34</v>
       </c>
       <c r="F9" t="n">
-        <v>4417</v>
+        <v>2667</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-353</v>
+        <v>-162</v>
       </c>
       <c r="H9" t="n">
-        <v>-1560</v>
+        <v>1203</v>
       </c>
       <c r="I9" t="n">
-        <v>60</v>
+        <v>-157</v>
       </c>
       <c r="J9" t="n">
-        <v>1113</v>
+        <v>164</v>
       </c>
       <c r="K9" t="n">
-        <v>200</v>
+        <v>59</v>
       </c>
       <c r="L9" t="n">
-        <v>2058</v>
+        <v>3137</v>
       </c>
       <c r="M9" t="n">
-        <v>9146</v>
+        <v>12567</v>
       </c>
       <c r="N9" t="n">
-        <v>-89478</v>
-      </c>
-      <c r="O9" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106259</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1555,12 +1620,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1569,47 +1634,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3190</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>-3.77</v>
+        <v>2705</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>4.04</v>
       </c>
       <c r="F10" t="n">
-        <v>1918</v>
+        <v>4417</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-256</v>
+        <v>-353</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>-1097</v>
       </c>
       <c r="I10" t="n">
-        <v>-128</v>
+        <v>60</v>
       </c>
       <c r="J10" t="n">
-        <v>-36</v>
+        <v>941</v>
       </c>
       <c r="K10" t="n">
-        <v>99</v>
+        <v>200</v>
       </c>
       <c r="L10" t="n">
-        <v>5792</v>
+        <v>2058</v>
       </c>
       <c r="M10" t="n">
-        <v>29733</v>
+        <v>7250</v>
       </c>
       <c r="N10" t="n">
-        <v>-19740</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89478</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1644,13 +1701,13 @@
         <v>-4</v>
       </c>
       <c r="H11" t="n">
-        <v>433</v>
+        <v>23</v>
       </c>
       <c r="I11" t="n">
         <v>-5</v>
       </c>
       <c r="J11" t="n">
-        <v>-279</v>
+        <v>-275</v>
       </c>
       <c r="K11" t="n">
         <v>22</v>
@@ -1659,20 +1716,12 @@
         <v>4373</v>
       </c>
       <c r="M11" t="n">
-        <v>22778</v>
+        <v>18055</v>
       </c>
       <c r="N11" t="n">
         <v>-19322</v>
       </c>
-      <c r="O11" t="n">
-        <v>-4.09</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1681,61 +1730,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1485</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>3.12</v>
+        <v>6285</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-0.71</v>
       </c>
       <c r="F12" t="n">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>-2041</v>
+        <v>-577</v>
       </c>
       <c r="I12" t="n">
-        <v>-22</v>
+        <v>-3</v>
       </c>
       <c r="J12" t="n">
-        <v>1925</v>
+        <v>294</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
-        <v>-138</v>
+        <v>255</v>
       </c>
       <c r="M12" t="n">
-        <v>-96</v>
+        <v>997</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8986</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1744,12 +1785,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台新科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1758,44 +1799,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>134.5</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.13</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>937</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="H13" t="n">
-        <v>251</v>
+        <v>-1808</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-22</v>
       </c>
       <c r="J13" t="n">
-        <v>-501</v>
+        <v>1485</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>-138</v>
       </c>
       <c r="M13" t="n">
-        <v>-141</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1818,19 +1854,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>401.5</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3.61</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>3778</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>96</v>
       </c>
       <c r="H14" t="n">
-        <v>-216</v>
+        <v>-104</v>
       </c>
       <c r="I14" t="n">
         <v>-870</v>
@@ -1845,20 +1881,12 @@
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>-380</v>
+        <v>-561</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1867,12 +1895,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1881,44 +1909,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1310</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-2.96</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>449</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-183</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>801</v>
       </c>
       <c r="H15" t="n">
-        <v>-606</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-70</v>
+        <v>144</v>
       </c>
       <c r="K15" t="n">
-        <v>-24</v>
+        <v>-69</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>-102</v>
       </c>
       <c r="M15" t="n">
-        <v>-72</v>
+        <v>-373</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1927,475 +1947,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>184</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-0.54</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>3931</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>-18</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>-827</v>
+        <v>-45</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>58</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>11</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4298</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20948</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-11211</v>
-      </c>
-      <c r="O16" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1420</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-5.65</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6551</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-2430</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-812</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-142</v>
-      </c>
-      <c r="J17" t="n">
-        <v>842</v>
-      </c>
-      <c r="K17" t="n">
-        <v>109</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2056</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9125</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-140185</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>波若威</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>888</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1115</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>-143</v>
-      </c>
-      <c r="H18" t="n">
-        <v>93</v>
-      </c>
-      <c r="I18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" t="n">
-        <v>70</v>
-      </c>
-      <c r="K18" t="n">
-        <v>26</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-753</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1010</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2792</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>-1263</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-888</v>
-      </c>
-      <c r="I19" t="n">
-        <v>105</v>
-      </c>
-      <c r="J19" t="n">
-        <v>839</v>
-      </c>
-      <c r="K19" t="n">
-        <v>147</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2107</v>
-      </c>
-      <c r="M19" t="n">
-        <v>10133</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-47608</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>969</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1094</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>145</v>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>9</v>
-      </c>
-      <c r="M20" t="n">
-        <v>139</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>684</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1698</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>801</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-104</v>
-      </c>
-      <c r="J21" t="n">
-        <v>144</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-69</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-102</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-489</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>6285</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="E22" t="n">
-        <v>457</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-570</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>292</v>
-      </c>
-      <c r="J22" t="n">
-        <v>23</v>
-      </c>
-      <c r="K22" t="n">
-        <v>255</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1252</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-8986</v>
-      </c>
-      <c r="N22" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1530</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2667</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>-162</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1040</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-157</v>
-      </c>
-      <c r="I23" t="n">
-        <v>6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>59</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3137</v>
-      </c>
-      <c r="L23" t="n">
-        <v>15704</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-106259</v>
-      </c>
-      <c r="N23" t="n">
-        <v>20</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260313.xlsx
+++ b/outputs/monitor_xlsx/20260313.xlsx
@@ -544,10 +544,6 @@
           <t>-0.54%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.42%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+0.16%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-1.24%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.28%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+0.05%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-0.37%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+3.11%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-580.17億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-496.04億</t>
@@ -807,7 +769,6 @@
           <t>-0.44億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>47.91億</t>
@@ -818,8 +779,6 @@
           <t>239.53億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-673.42億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>15640口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>14687口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-64.03億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-12.59億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1116,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1295,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1303,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75.95</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-0.85</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>115111</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-58613</v>
       </c>
       <c r="H4" t="n">
-        <v>-331939</v>
+        <v>-390551</v>
       </c>
       <c r="I4" t="n">
         <v>65</v>
       </c>
       <c r="J4" t="n">
-        <v>13115</v>
+        <v>13180</v>
       </c>
       <c r="K4" t="n">
         <v>15007</v>
@@ -1331,11 +1273,14 @@
         <v>13375</v>
       </c>
       <c r="M4" t="n">
-        <v>54244</v>
+        <v>67619</v>
       </c>
       <c r="N4" t="n">
         <v>-4446750</v>
       </c>
+      <c r="O4" t="n">
+        <v>-0.78</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1358,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>921</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-0.11</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>2092</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-96</v>
       </c>
       <c r="H5" t="n">
-        <v>-632</v>
+        <v>-728</v>
       </c>
       <c r="I5" t="n">
         <v>-78</v>
       </c>
       <c r="J5" t="n">
-        <v>-568</v>
+        <v>-646</v>
       </c>
       <c r="K5" t="n">
         <v>75</v>
@@ -1386,11 +1331,14 @@
         <v>2789</v>
       </c>
       <c r="M5" t="n">
-        <v>11081</v>
+        <v>13870</v>
       </c>
       <c r="N5" t="n">
         <v>-78814</v>
       </c>
+      <c r="O5" t="n">
+        <v>-3.73</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1413,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>1385</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>1.09</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>7798</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>268</v>
       </c>
       <c r="H6" t="n">
-        <v>93</v>
+        <v>361</v>
       </c>
       <c r="I6" t="n">
         <v>-178</v>
       </c>
       <c r="J6" t="n">
-        <v>1365</v>
+        <v>1187</v>
       </c>
       <c r="K6" t="n">
         <v>210</v>
@@ -1441,11 +1389,14 @@
         <v>5871</v>
       </c>
       <c r="M6" t="n">
-        <v>23454</v>
+        <v>29325</v>
       </c>
       <c r="N6" t="n">
         <v>-648994</v>
       </c>
+      <c r="O6" t="n">
+        <v>6.37</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1468,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1865</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-1.06</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>36317</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-12743</v>
       </c>
       <c r="H7" t="n">
-        <v>-52825</v>
+        <v>-65568</v>
       </c>
       <c r="I7" t="n">
         <v>-133</v>
       </c>
       <c r="J7" t="n">
-        <v>3430</v>
+        <v>3297</v>
       </c>
       <c r="K7" t="n">
         <v>1133</v>
@@ -1496,11 +1447,14 @@
         <v>25620</v>
       </c>
       <c r="M7" t="n">
-        <v>99025</v>
+        <v>124645</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
+      <c r="O7" t="n">
+        <v>-1.14</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1523,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1420</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-5.65</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>6551</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-2430</v>
       </c>
       <c r="H8" t="n">
-        <v>-832</v>
+        <v>-3262</v>
       </c>
       <c r="I8" t="n">
         <v>-142</v>
       </c>
       <c r="J8" t="n">
-        <v>408</v>
+        <v>265</v>
       </c>
       <c r="K8" t="n">
         <v>109</v>
@@ -1551,11 +1505,14 @@
         <v>2056</v>
       </c>
       <c r="M8" t="n">
-        <v>7358</v>
+        <v>9414</v>
       </c>
       <c r="N8" t="n">
         <v>-140185</v>
       </c>
+      <c r="O8" t="n">
+        <v>3.09</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1578,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1530</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2.34</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>2667</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-162</v>
       </c>
       <c r="H9" t="n">
-        <v>1203</v>
+        <v>1040</v>
       </c>
       <c r="I9" t="n">
         <v>-157</v>
       </c>
       <c r="J9" t="n">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
         <v>59</v>
@@ -1606,11 +1563,14 @@
         <v>3137</v>
       </c>
       <c r="M9" t="n">
-        <v>12567</v>
+        <v>15704</v>
       </c>
       <c r="N9" t="n">
         <v>-106259</v>
       </c>
+      <c r="O9" t="n">
+        <v>21.16</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1633,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>2705</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>4.04</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>4417</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-353</v>
       </c>
       <c r="H10" t="n">
-        <v>-1097</v>
+        <v>-1450</v>
       </c>
       <c r="I10" t="n">
         <v>60</v>
       </c>
       <c r="J10" t="n">
-        <v>941</v>
+        <v>1001</v>
       </c>
       <c r="K10" t="n">
         <v>200</v>
@@ -1661,11 +1621,14 @@
         <v>2058</v>
       </c>
       <c r="M10" t="n">
-        <v>7250</v>
+        <v>9308</v>
       </c>
       <c r="N10" t="n">
         <v>-89478</v>
       </c>
+      <c r="O10" t="n">
+        <v>18.74</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1694,20 +1657,20 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>680</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-4</v>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I11" t="n">
         <v>-5</v>
       </c>
       <c r="J11" t="n">
-        <v>-275</v>
+        <v>-280</v>
       </c>
       <c r="K11" t="n">
         <v>22</v>
@@ -1716,11 +1679,14 @@
         <v>4373</v>
       </c>
       <c r="M11" t="n">
-        <v>18055</v>
+        <v>22428</v>
       </c>
       <c r="N11" t="n">
         <v>-19322</v>
       </c>
+      <c r="O11" t="n">
+        <v>-12.56</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1743,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>6285</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-0.71</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>457</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>-577</v>
+        <v>-570</v>
       </c>
       <c r="I12" t="n">
         <v>-3</v>
       </c>
       <c r="J12" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K12" t="n">
         <v>23</v>
@@ -1771,11 +1737,14 @@
         <v>255</v>
       </c>
       <c r="M12" t="n">
-        <v>997</v>
+        <v>1252</v>
       </c>
       <c r="N12" t="n">
         <v>-8986</v>
       </c>
+      <c r="O12" t="n">
+        <v>24.81</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>151</v>
       </c>
       <c r="H13" t="n">
-        <v>-1808</v>
+        <v>-1657</v>
       </c>
       <c r="I13" t="n">
         <v>-22</v>
       </c>
       <c r="J13" t="n">
-        <v>1485</v>
+        <v>1463</v>
       </c>
       <c r="K13" t="n">
         <v>35</v>
@@ -1826,11 +1795,14 @@
         <v>-138</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>-128</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>96</v>
       </c>
       <c r="H14" t="n">
-        <v>-104</v>
+        <v>-8</v>
       </c>
       <c r="I14" t="n">
         <v>-870</v>
       </c>
       <c r="J14" t="n">
-        <v>-774</v>
+        <v>-1644</v>
       </c>
       <c r="K14" t="n">
         <v>-22</v>
@@ -1881,11 +1853,14 @@
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>-561</v>
+        <v>-511</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1883,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>801</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>819</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>144</v>
@@ -1933,11 +1911,14 @@
         <v>-102</v>
       </c>
       <c r="M15" t="n">
-        <v>-373</v>
+        <v>-475</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1960,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>-45</v>
+        <v>-44</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
@@ -1985,15 +1969,71 @@
         <v>9</v>
       </c>
       <c r="M16" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>390.5</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>8981</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>438</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1640</v>
+      </c>
+      <c r="I17" t="n">
+        <v>83</v>
+      </c>
+      <c r="J17" t="n">
+        <v>637</v>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8898</v>
+      </c>
+      <c r="M17" t="n">
+        <v>37990</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-21818</v>
+      </c>
+      <c r="O17" t="n">
+        <v>37.43</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260313.xlsx
+++ b/outputs/monitor_xlsx/20260313.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>37.43</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1720</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7254</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-3479</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-8022</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-194</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-188</v>
+      </c>
+      <c r="K18" t="n">
+        <v>353</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29068</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400945</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>508</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21131</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>4855</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12574</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-401</v>
+      </c>
+      <c r="K19" t="n">
+        <v>483</v>
+      </c>
+      <c r="L19" t="n">
+        <v>36559</v>
+      </c>
+      <c r="M19" t="n">
+        <v>183047</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-392418</v>
+      </c>
+      <c r="O19" t="n">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>515</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3385</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>485</v>
+      </c>
+      <c r="H20" t="n">
+        <v>776</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-191</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-250</v>
+      </c>
+      <c r="K20" t="n">
+        <v>264</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8740</v>
+      </c>
+      <c r="M20" t="n">
+        <v>44568</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161519</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.960000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
